--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AUTOCARES RODRÍGUEZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AUTOCARES RODRÍGUEZ.xlsx
@@ -565,13 +565,13 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>45.7057</v>
+        <v>33.77</v>
       </c>
       <c r="E2" t="n">
-        <v>43.7807</v>
+        <v>30.0141</v>
       </c>
       <c r="F2" t="n">
-        <v>1.924899999999999</v>
+        <v>3.755699999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.684000000000001</v>
@@ -610,13 +610,13 @@
         <v>39.9708</v>
       </c>
       <c r="S2" t="n">
-        <v>21.113</v>
+        <v>9.177199999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>21.3998</v>
+        <v>7.6333</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2870999999999999</v>
+        <v>1.5439</v>
       </c>
       <c r="V2" t="n">
         <v>-5.315399999999999</v>
@@ -643,13 +643,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>28.4633</v>
+        <v>15.162</v>
       </c>
       <c r="E3" t="n">
-        <v>17.9687</v>
+        <v>6.341100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4947</v>
+        <v>8.821099999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-3.099700000000001</v>
@@ -688,13 +688,13 @@
         <v>28.1347</v>
       </c>
       <c r="S3" t="n">
-        <v>23.5145</v>
+        <v>10.2133</v>
       </c>
       <c r="T3" t="n">
-        <v>17.6901</v>
+        <v>6.0626</v>
       </c>
       <c r="U3" t="n">
-        <v>5.8247</v>
+        <v>4.1508</v>
       </c>
       <c r="V3" t="n">
         <v>4.168100000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8877</v>
+        <v>2.7213</v>
       </c>
       <c r="E4" t="n">
-        <v>1.407</v>
+        <v>1.5677</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4807</v>
+        <v>1.1537</v>
       </c>
       <c r="G4" t="n">
         <v>2.1045</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7407</v>
+        <v>-0.9071</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.9295</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3495</v>
+        <v>0.0225</v>
       </c>
       <c r="V4" t="n">
         <v>0.9418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1659000000000002</v>
+        <v>-0.6909999999999989</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5708</v>
+        <v>10.7004</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7367</v>
+        <v>-11.3917</v>
       </c>
       <c r="G5" t="n">
-        <v>-14.7838</v>
+        <v>-20.8066</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.6333</v>
+        <v>-3.4149</v>
       </c>
       <c r="I5" t="n">
-        <v>-12.1509</v>
+        <v>-17.3919</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1667000000000002</v>
+        <v>32.8474</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1894999999999999</v>
+        <v>23.2054</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02289999999999998</v>
+        <v>9.6419</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.6174</v>
+        <v>-53.6537</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.4438</v>
+        <v>-26.6198</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.1737</v>
+        <v>-27.034</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9105</v>
+        <v>-2.328499999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.866</v>
+        <v>-61.12029999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>13.7762</v>
+        <v>58.7916</v>
       </c>
       <c r="S5" t="n">
-        <v>14.2985</v>
+        <v>-6.2818</v>
       </c>
       <c r="T5" t="n">
-        <v>11.5272</v>
+        <v>-6.287199999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7713</v>
+        <v>0.005399999999999933</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5911</v>
+        <v>28.7254</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0762</v>
+        <v>45.2606</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.667</v>
+        <v>-16.5349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTÍN FERNÁNDEZ</t>
+          <t>C. DIN PENDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7328999999999999</v>
+        <v>-1.0432</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.24</v>
+        <v>-1.3487</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5071</v>
+        <v>0.3055</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8036</v>
+        <v>-2.5458</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8115000000000001</v>
+        <v>-1.9896</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9922</v>
+        <v>-0.5561999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9084</v>
+        <v>-0.1808000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6549</v>
+        <v>0.3420000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2534</v>
+        <v>-0.5226999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1048</v>
+        <v>-2.3651</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1566</v>
+        <v>-2.3316</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2614</v>
+        <v>-0.03349999999999997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.9105</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.9105</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.5468000000000001</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.6684</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.1216</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.3299</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.3299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. DIN PENDA</t>
+          <t>S. KIMOTO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5765</v>
+        <v>-1.0555</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6095</v>
+        <v>-1.443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03290000000000004</v>
+        <v>0.3873999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5458</v>
+        <v>-1.6914</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9896</v>
+        <v>-2.7417</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5561999999999999</v>
+        <v>1.0504</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1808000000000001</v>
+        <v>4.7472</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3420000000000002</v>
+        <v>1.4667</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5226999999999999</v>
+        <v>3.2807</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3651</v>
+        <v>-6.4386</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3316</v>
+        <v>-4.2083</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03349999999999997</v>
+        <v>-2.2301</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-6.015</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-11.0598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9105</v>
+        <v>5.0449</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2546</v>
+        <v>1.1253</v>
       </c>
       <c r="T7" t="n">
-        <v>0.258</v>
+        <v>0.0696</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5125</v>
+        <v>1.0554</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2239</v>
+        <v>5.525700000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2239</v>
+        <v>4.8</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KIMOTO</t>
+          <t>A. MARTÍN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2131</v>
+        <v>-1.3156</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.066599999999999</v>
+        <v>-2.0408</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8536000000000004</v>
+        <v>0.7252000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6914</v>
+        <v>-1.8036</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7417</v>
+        <v>-0.8115000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0504</v>
+        <v>-0.9922</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7472</v>
+        <v>-1.9084</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4667</v>
+        <v>-0.6549</v>
       </c>
       <c r="L8" t="n">
-        <v>3.2807</v>
+        <v>-1.2534</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.4386</v>
+        <v>0.1048</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.2083</v>
+        <v>-0.1566</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2301</v>
+        <v>0.2614</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.015</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.0598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5.0449</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0321</v>
+        <v>-0.03589999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.554</v>
+        <v>-0.1324</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5216</v>
+        <v>0.0965</v>
       </c>
       <c r="V8" t="n">
-        <v>5.525700000000001</v>
+        <v>0.3299</v>
       </c>
       <c r="W8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7257</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5744</v>
+        <v>-2.9049</v>
       </c>
       <c r="E9" t="n">
-        <v>1.64</v>
+        <v>1.6611</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.214499999999999</v>
+        <v>-4.566</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4351</v>
@@ -1156,13 +1156,13 @@
         <v>5.4328</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2537</v>
+        <v>0.4158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2737000000000001</v>
+        <v>-0.2527</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02009999999999993</v>
+        <v>0.6685</v>
       </c>
       <c r="V9" t="n">
         <v>-3.9901</v>
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6398</v>
+        <v>-3.0604</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2789</v>
+        <v>-0.7784</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3609</v>
+        <v>-2.2819</v>
       </c>
       <c r="G10" t="n">
         <v>0.5044999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>3.8806</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3905</v>
+        <v>-1.811</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.3811000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5088</v>
+        <v>-1.4299</v>
       </c>
       <c r="V10" t="n">
         <v>0.1865999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5473</v>
+        <v>-4.4321</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4545</v>
+        <v>0.3544</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.001799999999999</v>
+        <v>-4.7865</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2011</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04329999999999998</v>
+        <v>0.1584</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6201</v>
+        <v>0.52</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.577</v>
+        <v>-0.3617</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1656</v>
@@ -1345,13 +1345,13 @@
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.144600000000001</v>
+        <v>-5.4657</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.107</v>
+        <v>-3.4468</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0378</v>
+        <v>-2.018999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-9.915699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>8.5374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.01109999999999994</v>
+        <v>-0.332</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.634</v>
+        <v>-0.9738000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6226999999999999</v>
+        <v>0.6417</v>
       </c>
       <c r="V12" t="n">
         <v>-1.815</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.3609</v>
+        <v>-7.818499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.183200000000001</v>
+        <v>-5.9155</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.5445</v>
+        <v>-1.9031</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.8137</v>
+        <v>-14.7838</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7075999999999993</v>
+        <v>-2.6333</v>
       </c>
       <c r="I13" t="n">
-        <v>-16.5214</v>
+        <v>-12.1509</v>
       </c>
       <c r="J13" t="n">
-        <v>13.0807</v>
+        <v>-0.1667000000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>13.2687</v>
+        <v>-0.1894999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1877</v>
+        <v>0.02289999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-28.8946</v>
+        <v>-14.6174</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.5609</v>
+        <v>-2.4438</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.3336</v>
+        <v>-12.1737</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5523</v>
+        <v>2.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.0152</v>
+        <v>-10.866</v>
       </c>
       <c r="R13" t="n">
-        <v>20.5674</v>
+        <v>13.7762</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6136</v>
+        <v>6.6458</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2939</v>
+        <v>4.0409</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6803</v>
+        <v>2.6051</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2865999999999997</v>
+        <v>-2.5911</v>
       </c>
       <c r="W13" t="n">
-        <v>10.8239</v>
+        <v>1.0762</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.5373</v>
+        <v>-3.667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.9367</v>
+        <v>-15.2053</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.805600000000005</v>
+        <v>4.320399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.130800000000001</v>
+        <v>-19.5256</v>
       </c>
       <c r="G14" t="n">
-        <v>-52.199</v>
+        <v>-15.8137</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.8123</v>
+        <v>0.7075999999999993</v>
       </c>
       <c r="I14" t="n">
-        <v>-37.3863</v>
+        <v>-16.5214</v>
       </c>
       <c r="J14" t="n">
-        <v>5.773099999999999</v>
+        <v>13.0807</v>
       </c>
       <c r="K14" t="n">
-        <v>15.6584</v>
+        <v>13.2687</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.8855</v>
+        <v>-0.1877</v>
       </c>
       <c r="M14" t="n">
-        <v>-57.9721</v>
+        <v>-28.8946</v>
       </c>
       <c r="N14" t="n">
-        <v>-30.4706</v>
+        <v>-12.5609</v>
       </c>
       <c r="O14" t="n">
-        <v>-27.5014</v>
+        <v>-16.3336</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7761000000000002</v>
+        <v>1.5523</v>
       </c>
       <c r="Q14" t="n">
-        <v>-63.2545</v>
+        <v>-19.0152</v>
       </c>
       <c r="R14" t="n">
-        <v>64.0304</v>
+        <v>20.5674</v>
       </c>
       <c r="S14" t="n">
-        <v>15.2514</v>
+        <v>-1.2301</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.190999999999999</v>
+        <v>-0.5689</v>
       </c>
       <c r="U14" t="n">
-        <v>18.4422</v>
+        <v>-0.6615000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>19.2346</v>
+        <v>0.2865999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>51.8665</v>
+        <v>10.8239</v>
       </c>
       <c r="X14" t="n">
-        <v>-32.6321</v>
+        <v>-10.5373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>R. DEUS VERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.2655</v>
+        <v>-18.1689</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.9092</v>
+        <v>-10.2768</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.356399999999999</v>
+        <v>-7.892100000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8861</v>
+        <v>-11.5367</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6048</v>
+        <v>-6.422000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2813</v>
+        <v>-5.1147</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7883</v>
+        <v>-3.7304</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7437</v>
+        <v>-2.4921</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0447</v>
+        <v>-1.2384</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.674799999999999</v>
+        <v>-7.8063</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.3486</v>
+        <v>-3.93</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3257</v>
+        <v>-3.8763</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.7911</v>
+        <v>-0.1940999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-22.5078</v>
+        <v>-5.0448</v>
       </c>
       <c r="R15" t="n">
-        <v>15.7165</v>
+        <v>4.8508</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6963</v>
+        <v>-2.5322</v>
       </c>
       <c r="T15" t="n">
-        <v>4.1057</v>
+        <v>-0.4642</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4091</v>
+        <v>-2.0681</v>
       </c>
       <c r="V15" t="n">
-        <v>-11.2846</v>
+        <v>-3.9059</v>
       </c>
       <c r="W15" t="n">
-        <v>4.704499999999999</v>
+        <v>-1.0373</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.9891</v>
+        <v>-2.8686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. DEUS VERA</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>-19.2148</v>
+        <v>-19.3799</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.8378</v>
+        <v>-11.5497</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.376999999999999</v>
+        <v>-7.8303</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.5367</v>
+        <v>-1.8861</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.422000000000001</v>
+        <v>-1.6048</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.1147</v>
+        <v>-0.2813</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.7304</v>
+        <v>5.7883</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4921</v>
+        <v>2.7437</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2384</v>
+        <v>3.0447</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.8063</v>
+        <v>-7.674799999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.93</v>
+        <v>-4.3486</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.8763</v>
+        <v>-3.3257</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1940999999999999</v>
+        <v>-6.7911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.0448</v>
+        <v>-22.5078</v>
       </c>
       <c r="R16" t="n">
-        <v>4.8508</v>
+        <v>15.7165</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.5782</v>
+        <v>0.5820999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0253</v>
+        <v>0.4649999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.553</v>
+        <v>0.1168</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.9059</v>
+        <v>-11.2846</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.0373</v>
+        <v>4.704499999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.8686</v>
+        <v>-15.9891</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-20.6401</v>
+        <v>-24.3968</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.261299999999997</v>
+        <v>-12.2929</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.3784</v>
+        <v>-12.1039</v>
       </c>
       <c r="G17" t="n">
-        <v>-20.8066</v>
+        <v>-23.0179</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.4149</v>
+        <v>-9.6351</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.3919</v>
+        <v>-13.3824</v>
       </c>
       <c r="J17" t="n">
-        <v>32.8474</v>
+        <v>-2.253200000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>23.2054</v>
+        <v>1.5862</v>
       </c>
       <c r="L17" t="n">
-        <v>9.6419</v>
+        <v>-3.8391</v>
       </c>
       <c r="M17" t="n">
-        <v>-53.6537</v>
+        <v>-20.7645</v>
       </c>
       <c r="N17" t="n">
-        <v>-26.6198</v>
+        <v>-11.2214</v>
       </c>
       <c r="O17" t="n">
-        <v>-27.034</v>
+        <v>-9.543199999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.328499999999999</v>
+        <v>6.5969</v>
       </c>
       <c r="Q17" t="n">
-        <v>-61.12029999999999</v>
+        <v>-12.4183</v>
       </c>
       <c r="R17" t="n">
-        <v>58.7916</v>
+        <v>19.0151</v>
       </c>
       <c r="S17" t="n">
-        <v>-26.2306</v>
+        <v>-1.7388</v>
       </c>
       <c r="T17" t="n">
-        <v>-21.2493</v>
+        <v>-1.7621</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.9815</v>
+        <v>0.02309999999999993</v>
       </c>
       <c r="V17" t="n">
-        <v>28.7254</v>
+        <v>-6.237200000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>45.2606</v>
+        <v>4.1403</v>
       </c>
       <c r="X17" t="n">
-        <v>-16.5349</v>
+        <v>-10.3775</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-28.8119</v>
+        <v>-26.3907</v>
       </c>
       <c r="E18" t="n">
-        <v>-16.2994</v>
+        <v>-7.296399999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.5123</v>
+        <v>-19.0941</v>
       </c>
       <c r="G18" t="n">
-        <v>-23.0179</v>
+        <v>-52.199</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.6351</v>
+        <v>-14.8123</v>
       </c>
       <c r="I18" t="n">
-        <v>-13.3824</v>
+        <v>-37.3863</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.253200000000001</v>
+        <v>5.773099999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5862</v>
+        <v>15.6584</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.8391</v>
+        <v>-9.8855</v>
       </c>
       <c r="M18" t="n">
-        <v>-20.7645</v>
+        <v>-57.9721</v>
       </c>
       <c r="N18" t="n">
-        <v>-11.2214</v>
+        <v>-30.4706</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.543199999999999</v>
+        <v>-27.5014</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5969</v>
+        <v>0.7761000000000002</v>
       </c>
       <c r="Q18" t="n">
-        <v>-12.4183</v>
+        <v>-63.2545</v>
       </c>
       <c r="R18" t="n">
-        <v>19.0151</v>
+        <v>64.0304</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.1541</v>
+        <v>5.7974</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.7687</v>
+        <v>-1.6819</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3854999999999998</v>
+        <v>7.4793</v>
       </c>
       <c r="V18" t="n">
-        <v>-6.237200000000001</v>
+        <v>19.2346</v>
       </c>
       <c r="W18" t="n">
-        <v>4.1403</v>
+        <v>51.8665</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.3775</v>
+        <v>-32.6321</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-51.7725</v>
+        <v>-42.1148</v>
       </c>
       <c r="E19" t="n">
-        <v>-53.9667</v>
+        <v>-46.7966</v>
       </c>
       <c r="F19" t="n">
-        <v>2.193900000000001</v>
+        <v>4.6815</v>
       </c>
       <c r="G19" t="n">
         <v>-25.825</v>
@@ -1936,13 +1936,13 @@
         <v>34.7321</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.455</v>
+        <v>-1.7971</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.9217</v>
+        <v>-1.7515</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.5337</v>
+        <v>-0.04589999999999994</v>
       </c>
       <c r="V19" t="n">
         <v>0.06030000000000002</v>
@@ -1969,13 +1969,13 @@
         <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>-58.8749</v>
+        <v>-47.0544</v>
       </c>
       <c r="E20" t="n">
-        <v>-42.2786</v>
+        <v>-35.7645</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.5963</v>
+        <v>-11.2899</v>
       </c>
       <c r="G20" t="n">
         <v>-22.9229</v>
@@ -2014,13 +2014,13 @@
         <v>36.2842</v>
       </c>
       <c r="S20" t="n">
-        <v>-21.0341</v>
+        <v>-9.213699999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.062</v>
+        <v>-5.5477</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.972300000000001</v>
+        <v>-3.6661</v>
       </c>
       <c r="V20" t="n">
         <v>-6.3807</v>
@@ -2047,13 +2047,13 @@
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>-75.8582</v>
+        <v>-61.3792</v>
       </c>
       <c r="E21" t="n">
-        <v>-59.4789</v>
+        <v>-48.4812</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.3794</v>
+        <v>-12.8979</v>
       </c>
       <c r="G21" t="n">
         <v>-29.2975</v>
@@ -2092,13 +2092,13 @@
         <v>41.3288</v>
       </c>
       <c r="S21" t="n">
-        <v>-16.869</v>
+        <v>-2.3901</v>
       </c>
       <c r="T21" t="n">
-        <v>-14.1077</v>
+        <v>-3.1102</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.7613</v>
+        <v>0.7201</v>
       </c>
       <c r="V21" t="n">
         <v>1.547200000000001</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-246.2733</v>
+        <v>-230.2236</v>
       </c>
       <c r="E22" t="n">
-        <v>-139.1346</v>
+        <v>-132.4721</v>
       </c>
       <c r="F22" t="n">
-        <v>-107.139</v>
+        <v>-97.75190000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-235.4886</v>
@@ -2161,7 +2161,7 @@
         <v>-165.5075</v>
       </c>
       <c r="P22" t="n">
-        <v>-19.40409999999999</v>
+        <v>-19.4041</v>
       </c>
       <c r="Q22" t="n">
         <v>-425.9021</v>
@@ -2170,16 +2170,16 @@
         <v>406.4974</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.926299999999987</v>
+        <v>6.124199999999998</v>
       </c>
       <c r="T22" t="n">
-        <v>-11.19599999999999</v>
+        <v>-4.533099999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>1.268399999999998</v>
+        <v>10.6559</v>
       </c>
       <c r="V22" t="n">
-        <v>18.54450000000001</v>
+        <v>18.5445</v>
       </c>
       <c r="W22" t="n">
         <v>180.0625</v>
